--- a/AAII_Financials/Yearly/DK_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/DK_YR_FIN.xlsx
@@ -1455,16 +1455,16 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-7400</v>
+        <v>-6800</v>
       </c>
       <c r="E24" s="3">
-        <v>-79200</v>
+        <v>-107900</v>
       </c>
       <c r="F24" s="3">
-        <v>5100</v>
+        <v>-3000</v>
       </c>
       <c r="G24" s="3">
-        <v>63900</v>
+        <v>56400</v>
       </c>
       <c r="H24" s="3">
         <v>-42000</v>
@@ -1557,16 +1557,16 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>46300</v>
+        <v>45700</v>
       </c>
       <c r="E26" s="3">
-        <v>-626800</v>
+        <v>-598100</v>
       </c>
       <c r="F26" s="3">
-        <v>11500</v>
+        <v>19600</v>
       </c>
       <c r="G26" s="3">
-        <v>257900</v>
+        <v>265400</v>
       </c>
       <c r="H26" s="3">
         <v>-95300</v>
@@ -1710,16 +1710,16 @@
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>-3000</v>
+        <v>-2400</v>
       </c>
       <c r="E29" s="3">
-        <v>105900</v>
+        <v>77200</v>
       </c>
       <c r="F29" s="3">
-        <v>35200</v>
+        <v>27100</v>
       </c>
       <c r="G29" s="3">
-        <v>32600</v>
+        <v>25100</v>
       </c>
       <c r="H29" s="3">
         <v>0</v>
